--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.29771623873847</v>
+        <v>6.223378888795002</v>
       </c>
       <c r="D2" t="n">
-        <v>38.15686610911907</v>
+        <v>6.20049074273185</v>
       </c>
       <c r="E2" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F2" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.70426633791509</v>
+        <v>6.451943279911203</v>
       </c>
       <c r="D3" t="n">
-        <v>40.02317384271822</v>
+        <v>6.50376574944171</v>
       </c>
       <c r="E3" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F3" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.94940010300088</v>
+        <v>6.491777516737643</v>
       </c>
       <c r="D4" t="n">
-        <v>39.74961865695139</v>
+        <v>6.459313031754601</v>
       </c>
       <c r="E4" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F4" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.78357910389273</v>
+        <v>2.077331604382569</v>
       </c>
       <c r="D5" t="n">
-        <v>12.75948649802673</v>
+        <v>2.073416555929343</v>
       </c>
       <c r="E5" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F5" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.15957855863237</v>
+        <v>4.250931515777761</v>
       </c>
       <c r="D6" t="n">
-        <v>26.0898896527571</v>
+        <v>4.239607068573028</v>
       </c>
       <c r="E6" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F6" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.18894550726277</v>
+        <v>6.043203644930201</v>
       </c>
       <c r="D7" t="n">
-        <v>37.1708285005291</v>
+        <v>6.04025963133598</v>
       </c>
       <c r="E7" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F7" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76.80904168745523</v>
+        <v>12.48146927421148</v>
       </c>
       <c r="D8" t="n">
-        <v>19.30208699354667</v>
+        <v>3.136589136451335</v>
       </c>
       <c r="E8" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F8" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.44564701334346</v>
+        <v>6.247417639668313</v>
       </c>
       <c r="D9" t="n">
-        <v>38.45653719401779</v>
+        <v>6.249187294027891</v>
       </c>
       <c r="E9" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F9" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>82.48008105342865</v>
+        <v>13.40301317118216</v>
       </c>
       <c r="D10" t="n">
-        <v>30.40204572469598</v>
+        <v>4.940332430263098</v>
       </c>
       <c r="E10" t="n">
-        <v>21.06226339622701</v>
+        <v>3.42261780188689</v>
       </c>
       <c r="F10" t="n">
-        <v>9.403441951514493</v>
+        <v>1.528059317121105</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
